--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2019_aysen_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2019_aysen_provincial.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 11:21</t>
+    <t xml:space="preserve">2026-09-09 18:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2019_aysen_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2019_aysen_provincial.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 18:59</t>
+    <t xml:space="preserve">2026-09-17 04:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2019_aysen_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2019_aysen_provincial.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 04:17</t>
+    <t xml:space="preserve">2026-09-25 11:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2019_aysen_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2019_aysen_provincial.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-25 11:11</t>
+    <t xml:space="preserve">2026-09-26 23:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dependencia/plot_regional_d_deptot_a_2019_aysen_provincial.xlsx
+++ b/output/graficos_dependencia/plot_regional_d_deptot_a_2019_aysen_provincial.xlsx
@@ -48,7 +48,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-26 23:45</t>
+    <t xml:space="preserve">2026-10-05 04:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
-    <t xml:space="preserve">Region de Aysen</t>
+    <t xml:space="preserve">Region de Aysén</t>
   </si>
   <si>
     <t xml:space="preserve">Año</t>
